--- a/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno4/anno4_task3_question_quality.xlsx
+++ b/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno4/anno4_task3_question_quality.xlsx
@@ -1,21 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F6BEAE-142A-4128-BF8B-01CF711DDCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90652A0B-748B-4548-80D4-2A321E15488D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="159">
   <si>
     <t>UID</t>
   </si>
@@ -56,46 +70,46 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>SFTANNO-000021-0003</t>
-  </si>
-  <si>
-    <t>Have you heard about the possibility of black holes existing at the beginning of the universe?</t>
-  </si>
-  <si>
-    <t>Do you think we'll ever be able to understand everything about black holes?</t>
-  </si>
-  <si>
-    <t>Do you think we'll ever be able to travel to a black hole?</t>
-  </si>
-  <si>
-    <t>Do you think we'll ever be able to prove or disprove the existence of black holes at the beginning of the universe?</t>
-  </si>
-  <si>
-    <t>Do you think it's possible that black holes could help us understand the origins of the universe?</t>
-  </si>
-  <si>
-    <t>Do you think we'll ever be able to fully understand the mysteries of the universe?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000052-0003</t>
-  </si>
-  <si>
-    <t>I wish I had learned to play an instrument when I was younger.</t>
-  </si>
-  <si>
-    <t>Have you ever tried taking music lessons?</t>
-  </si>
-  <si>
-    <t>Have you considered taking lessons?</t>
-  </si>
-  <si>
-    <t>Have you considered taking online lessons?</t>
-  </si>
-  <si>
-    <t>What instrument are you thinking of learning?</t>
-  </si>
-  <si>
-    <t>Have you thought about which instrument you'd like to learn?</t>
+    <t>SFTANNO-000013-0003</t>
+  </si>
+  <si>
+    <t>I've never really thought about it, but I'm interested in exploring more.</t>
+  </si>
+  <si>
+    <t>Have you looked into any other ballets yet?</t>
+  </si>
+  <si>
+    <t>Have you considered looking up any ballet companies in your area?</t>
+  </si>
+  <si>
+    <t>Would you like some recommendations on where to start?</t>
+  </si>
+  <si>
+    <t>Have you ever seen a modern ballet?</t>
+  </si>
+  <si>
+    <t>Do you have any questions about ballet or the performances you're planning to see?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000182-0003</t>
+  </si>
+  <si>
+    <t>The Holocaust, because I want to understand how such devastation could happen.</t>
+  </si>
+  <si>
+    <t>Have you read any books about the Holocaust?</t>
+  </si>
+  <si>
+    <t>Have you ever visited any historical landmarks or sites?</t>
+  </si>
+  <si>
+    <t>Do you think history education should be more comprehensive?</t>
+  </si>
+  <si>
+    <t>Have you read any books on the Holocaust that you would recommend?</t>
+  </si>
+  <si>
+    <t>Have you read any good books about the Holocaust?</t>
   </si>
   <si>
     <t>SFTANNO-000019-0003</t>
@@ -161,43 +175,46 @@
     <t>Do you think there's anything we can do to help those affected?</t>
   </si>
   <si>
-    <t>SFTANNO-000049-0003</t>
-  </si>
-  <si>
-    <t>The director just announced a new initiative, and I'm genuinely surprised.</t>
-  </si>
-  <si>
-    <t>What's the new initiative all about?</t>
-  </si>
-  <si>
-    <t>How do you think this new initiative will affect the team?</t>
-  </si>
-  <si>
-    <t>What do you think about the initiative?</t>
-  </si>
-  <si>
-    <t>Do you think it will have a positive impact?</t>
-  </si>
-  <si>
-    <t>How do you think it will impact the company?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000008-0003</t>
-  </si>
-  <si>
-    <t>I've been thinking about volunteering at an animal shelter. It's a cause that's close to my heart.</t>
-  </si>
-  <si>
-    <t>Have you looked into any local shelters?</t>
-  </si>
-  <si>
-    <t>How can I help?</t>
-  </si>
-  <si>
-    <t>Have you looked into any shelters in your area?</t>
-  </si>
-  <si>
-    <t>Have you decided which shelter to volunteer at?</t>
+    <t>SFTANNO-000156-0003</t>
+  </si>
+  <si>
+    <t>There are! You can start with small changes, like rearranging furniture or adding plants to boost the energy in your space.</t>
+  </si>
+  <si>
+    <t>What are some Feng Shui principles you follow in your own home?</t>
+  </si>
+  <si>
+    <t>Is there anything I can do to feel more confident about it?</t>
+  </si>
+  <si>
+    <t>Do you have any other suggestions for making Feng Shui more manageable?</t>
+  </si>
+  <si>
+    <t>Is there a way to avoid that?</t>
+  </si>
+  <si>
+    <t>What kind of plants would you recommend for beginners?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000007-0003</t>
+  </si>
+  <si>
+    <t>They actually offered me the job!</t>
+  </si>
+  <si>
+    <t>Have you discussed your compensation package with the employer?</t>
+  </si>
+  <si>
+    <t>Have you thought about negotiating your salary or benefits?</t>
+  </si>
+  <si>
+    <t>What are your thoughts on the job offer?</t>
+  </si>
+  <si>
+    <t>Have you thought about negotiating your salary and benefits?</t>
+  </si>
+  <si>
+    <t>Have you started thinking about when you want to start?</t>
   </si>
   <si>
     <t>SFTANNO-000025-0003</t>
@@ -221,142 +238,145 @@
     <t>Do you have any other concerns or questions?</t>
   </si>
   <si>
-    <t>SFTANNO-000054-0003</t>
-  </si>
-  <si>
-    <t>I'm really into rap music, especially conscious hip-hop that tackles social issues.</t>
-  </si>
-  <si>
-    <t>Who are some of your favorite conscious hip-hop artists?</t>
-  </si>
-  <si>
-    <t>What are some of your favorite conscious hip-hop artists?</t>
-  </si>
-  <si>
-    <t>What are some of your favorite conscious hip-hop songs?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000005-0003</t>
-  </si>
-  <si>
-    <t>I'm so happy with my new prescription sunglasses. They make everything so much clearer!</t>
-  </si>
-  <si>
-    <t>Have you tried any new styles lately?</t>
-  </si>
-  <si>
-    <t>Do you have a favorite brand or style?</t>
-  </si>
-  <si>
-    <t>Have you tried any other types of sunglasses before?</t>
-  </si>
-  <si>
-    <t>Have you tried any other brands or styles?</t>
-  </si>
-  <si>
-    <t>What brand did you get them from?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000020-0003</t>
-  </si>
-  <si>
-    <t>I worry that exploring black holes could be dangerous for us and for our machines.</t>
-  </si>
-  <si>
-    <t>What do you think we should prioritize in the search for new discoveries?</t>
-  </si>
-  <si>
-    <t>What do you think the future holds for black hole research?</t>
-  </si>
-  <si>
-    <t>What do you think the future of black hole research will look like?</t>
-  </si>
-  <si>
-    <t>What do you think the biggest challenge is in studying black holes?</t>
-  </si>
-  <si>
-    <t>What's your favorite black hole fact?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000029-0003</t>
-  </si>
-  <si>
-    <t>I can't stand when fashion magazines promote unrealistic body images.</t>
-  </si>
-  <si>
-    <t>What do you think about the fashion industry as a whole?</t>
-  </si>
-  <si>
-    <t>Have you found any fashion sources that promote body positivity?</t>
-  </si>
-  <si>
-    <t>Do you have any favorite ethical fashion brands?</t>
-  </si>
-  <si>
-    <t>Do you have any favorite body-positive fashion brands?</t>
-  </si>
-  <si>
-    <t>What are your thoughts on promoting diversity in fashion?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000060-0003</t>
-  </si>
-  <si>
-    <t>With so many people relying on social media for their news, it's concerning how easy it is for false information to spread.</t>
-  </si>
-  <si>
-    <t>Do you think social media platforms should do more to combat the spread of false information?</t>
-  </si>
-  <si>
-    <t>What are some ways you personally verify the accuracy of news stories?</t>
-  </si>
-  <si>
-    <t>How do you think we can combat the spread of false information on social media?</t>
-  </si>
-  <si>
-    <t>How do you think we can combat the spread of false information online?</t>
-  </si>
-  <si>
-    <t>Have you ever been a victim of false information being spread about you?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000046-0003</t>
-  </si>
-  <si>
-    <t>Yes, I tried boiling brussels sprouts, and they came out mushy.</t>
-  </si>
-  <si>
-    <t>Have you found any good methods for cooking vegetables that are easy to follow?</t>
-  </si>
-  <si>
-    <t>Have you tried roasting or sautéing brussels sprouts instead of boiling them?</t>
-  </si>
-  <si>
-    <t>Have you tried roasting or sautéing them instead?</t>
-  </si>
-  <si>
-    <t>Have you tried roasting brussels sprouts instead?</t>
-  </si>
-  <si>
-    <t>What's your favorite vegetable to cook?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000012-0003</t>
-  </si>
-  <si>
-    <t>It's sickening to hear about poachers targeting endangered species for their valuable parts.</t>
-  </si>
-  <si>
-    <t>Have you heard of any successful anti-poaching initiatives?</t>
-  </si>
-  <si>
-    <t>Have you heard of any organizations that are actively combating poaching?</t>
-  </si>
-  <si>
-    <t>Have you researched any conservation organizations that work to combat wildlife trafficking?</t>
-  </si>
-  <si>
-    <t>Have you ever supported any anti-poaching organizations or initiatives?</t>
+    <t>SFTANNO-000167-0003</t>
+  </si>
+  <si>
+    <t>Do you think we'll see the implementation of AI in our daily lives soon?</t>
+  </si>
+  <si>
+    <t>What do you think is the most exciting development in AI right now?</t>
+  </si>
+  <si>
+    <t>What do you think will be the first significant change we'll see in our daily lives?</t>
+  </si>
+  <si>
+    <t>What do you think will be the first area to see significant change?</t>
+  </si>
+  <si>
+    <t>What kind of AI implementation do you think will be the most beneficial to society?</t>
+  </si>
+  <si>
+    <t>Do you think there are any potential drawbacks?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000001-0003</t>
+  </si>
+  <si>
+    <t>I finished that book you recommended, and it was amazing!</t>
+  </si>
+  <si>
+    <t>What book was it and what did you enjoy about it?</t>
+  </si>
+  <si>
+    <t>Do you have any other recommendations?</t>
+  </si>
+  <si>
+    <t>What's your next book on your list?</t>
+  </si>
+  <si>
+    <t>Do you have any preferences or genres you're interested in?</t>
+  </si>
+  <si>
+    <t>What was your favorite part of the book?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000004-0003</t>
+  </si>
+  <si>
+    <t>I'm worried about my son's eyesight. He's been complaining about headaches lately.</t>
+  </si>
+  <si>
+    <t>Maybe we can look up some local eye doctors together.</t>
+  </si>
+  <si>
+    <t>Have you considered taking him to an eye doctor for a checkup?</t>
+  </si>
+  <si>
+    <t>Have you noticed any other symptoms?</t>
+  </si>
+  <si>
+    <t>It's important to take care of our eyesight.</t>
+  </si>
+  <si>
+    <t>Have you made an appointment for him yet?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000000-0003</t>
+  </si>
+  <si>
+    <t>You won't believe it! They killed off my favorite character, and I'm so mad about it!</t>
+  </si>
+  <si>
+    <t>Have you considered reading any other fantasy books in the meantime?</t>
+  </si>
+  <si>
+    <t>Have you thought about what you want to read next?</t>
+  </si>
+  <si>
+    <t>Have you tried talking to someone about it?</t>
+  </si>
+  <si>
+    <t>Have you thought about rereading the series?</t>
+  </si>
+  <si>
+    <t>What's your favorite scene in the book?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000190-0003</t>
+  </si>
+  <si>
+    <t>I'm afraid I'm becoming addicted to binge-watching.</t>
+  </si>
+  <si>
+    <t>How do you balance your TV watching with other activities?</t>
+  </si>
+  <si>
+    <t>Have you tried setting limits for yourself?</t>
+  </si>
+  <si>
+    <t>Have you tried setting a daily limit for watching?</t>
+  </si>
+  <si>
+    <t>Have you tried any TV shows that are less time-consuming?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000161-0003</t>
+  </si>
+  <si>
+    <t>Honestly, I just can't believe the company would put us through this unnecessary anxiety and tension.</t>
+  </si>
+  <si>
+    <t>Have you considered talking to any coworkers about taking action?</t>
+  </si>
+  <si>
+    <t>Have you considered talking to HR about your concerns?</t>
+  </si>
+  <si>
+    <t>Do you think it's worth talking to HR about the handling of this situation?</t>
+  </si>
+  <si>
+    <t>Have you considered reaching out to any other companies or exploring new job opportunities?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000003-0003</t>
+  </si>
+  <si>
+    <t>I have, but the thought of using someone else's lens disgusts me a little.</t>
+  </si>
+  <si>
+    <t>Do you have any recommendations for other lenses that I could try?</t>
+  </si>
+  <si>
+    <t>Have you tried using a lens cleaning kit?</t>
+  </si>
+  <si>
+    <t>Have you considered trying out different lenses to find the one that suits your needs?</t>
+  </si>
+  <si>
+    <t>Maybe you can look into buying a new lens?</t>
+  </si>
+  <si>
+    <t>Have you looked into buying a used lens online?</t>
   </si>
   <si>
     <t>SFTANNO-000018-0003</t>
@@ -377,43 +397,46 @@
     <t>Have you ever thought about studying astronomy?</t>
   </si>
   <si>
-    <t>SFTANNO-000010-0003</t>
-  </si>
-  <si>
-    <t>My pet rabbit passed away recently, and I'm struggling to cope with the loss.</t>
-  </si>
-  <si>
-    <t>Have you considered adopting another rabbit in the future?</t>
-  </si>
-  <si>
-    <t>Is there anything I can do to support you during this difficult time?</t>
-  </si>
-  <si>
-    <t>Do you have any cherished memories or photos of your rabbit that bring you comfort?</t>
-  </si>
-  <si>
-    <t>Have you considered joining a pet loss support group?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000081-0003</t>
-  </si>
-  <si>
-    <t>That's a great idea, but it's infuriating that it has to come to this.</t>
-  </si>
-  <si>
-    <t>How can we get started on organizing this event?</t>
-  </si>
-  <si>
-    <t>Let's get started. How can we spread the word about our event?</t>
-  </si>
-  <si>
-    <t>When were you thinking of organizing the event?</t>
-  </si>
-  <si>
-    <t>When can we start planning?</t>
-  </si>
-  <si>
-    <t>When do you think we can start planning this event?</t>
+    <t>SFTANNO-000002-0003</t>
+  </si>
+  <si>
+    <t>Not yet, everything is still uncertain due to the pandemic.</t>
+  </si>
+  <si>
+    <t>How do you stay motivated during these tough times?</t>
+  </si>
+  <si>
+    <t>Do you have any other projects in mind?</t>
+  </si>
+  <si>
+    <t>Have you considered virtual events or book clubs?</t>
+  </si>
+  <si>
+    <t>When do you plan to release your book?</t>
+  </si>
+  <si>
+    <t>Have you considered virtual events or book readings?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000172-0003</t>
+  </si>
+  <si>
+    <t>I've tried to explain, but it's disheartening when they don't even want to listen.</t>
+  </si>
+  <si>
+    <t>How do you cope with their disbelief?</t>
+  </si>
+  <si>
+    <t>Do you think there's a way to change their perspective?</t>
+  </si>
+  <si>
+    <t>Would you like me to help you write a post about mindfulness?</t>
+  </si>
+  <si>
+    <t>Have you found other mindfulness enthusiasts to share your experiences with?</t>
+  </si>
+  <si>
+    <t>Have you considered finding like-minded individuals to discuss mindfulness with?</t>
   </si>
   <si>
     <t>SFTANNO-000011-0003</t>
@@ -458,25 +481,31 @@
     <t>Have you considered borrowing a dress from a friend or family member?</t>
   </si>
   <si>
-    <t>SFTANNO-000032-0003</t>
-  </si>
-  <si>
-    <t>I just got a new watch that tracks my sleep patterns and heart rate!</t>
-  </si>
-  <si>
-    <t>Have you tried any other smartwatches?</t>
-  </si>
-  <si>
-    <t>Have you noticed any changes in your sleep or heart rate since wearing it?</t>
-  </si>
-  <si>
-    <t>Do you feel like it's been helpful in monitoring your health?</t>
-  </si>
-  <si>
-    <t>Have you seen any other wearable tech devices that interest you?</t>
-  </si>
-  <si>
-    <t>Do you have any recommendations for good fitness trackers?</t>
+    <t>SFTANNO-000176-0003</t>
+  </si>
+  <si>
+    <t>No, just a pot for the pasta and a pan for the sauce.</t>
+  </si>
+  <si>
+    <t>When should I start?</t>
+  </si>
+  <si>
+    <t>Have you tried any other easy recipes lately?</t>
+  </si>
+  <si>
+    <t>How long do you think it'll take to make?</t>
+  </si>
+  <si>
+    <t>Thanks for sharing this recipe with me.</t>
+  </si>
+  <si>
+    <t>Let me know if you need any more tips or help.</t>
+  </si>
+  <si>
+    <t>Falta contexto</t>
+  </si>
+  <si>
+    <t>Las preguntas no tienen mucho sentido ya que la persona no sabe del tema</t>
   </si>
 </sst>
 </file>
@@ -532,16 +561,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -846,24 +872,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="2" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="28.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="28.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="28.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="28.28515625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19.140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="28.28515625" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.88671875" style="2" customWidth="1"/>
+    <col min="2" max="3" width="27.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="27.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9" style="2" customWidth="1"/>
+    <col min="7" max="7" width="27.5546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.21875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="27.5546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8" style="2" customWidth="1"/>
+    <col min="11" max="11" width="27.5546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="8.33203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="4.109375" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -904,7 +930,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -914,35 +940,35 @@
       <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3">
-        <v>2</v>
+      <c r="D2" s="2">
+        <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="3">
-        <v>1</v>
+      <c r="F2" s="2">
+        <v>2</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3">
-        <v>5</v>
+      <c r="H2" s="2">
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="3">
-        <v>4</v>
+      <c r="J2" s="2">
+        <v>3</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="L2" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -952,35 +978,35 @@
       <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="3">
-        <v>4</v>
+      <c r="F3" s="2">
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>3</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="3">
-        <v>1</v>
+      <c r="J3" s="2">
+        <v>2</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="L3" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -990,35 +1016,35 @@
       <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="3">
-        <v>1</v>
+      <c r="D4" s="2">
+        <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="3">
-        <v>3</v>
+      <c r="F4" s="2">
+        <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>2</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>5</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="L4" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1028,35 +1054,35 @@
       <c r="C5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="3">
-        <v>3</v>
+      <c r="D5" s="2">
+        <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>5</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>2</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="3">
-        <v>4</v>
+      <c r="J5" s="2">
+        <v>1</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="L5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -1066,35 +1092,35 @@
       <c r="C6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="3">
-        <v>1</v>
+      <c r="D6" s="2">
+        <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="3">
-        <v>2</v>
+      <c r="H6" s="2">
+        <v>3</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="3">
-        <v>3</v>
+      <c r="J6" s="2">
+        <v>1</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="L6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
@@ -1104,35 +1130,35 @@
       <c r="C7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="3">
-        <v>4</v>
+      <c r="H7" s="2">
+        <v>3</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="3">
-        <v>3</v>
+      <c r="J7" s="2">
+        <v>4</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="L7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -1142,569 +1168,581 @@
       <c r="C8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="3">
-        <v>3</v>
+      <c r="D8" s="2">
+        <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="3">
-        <v>4</v>
+        <v>58</v>
+      </c>
+      <c r="F8" s="2">
+        <v>3</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="3">
-        <v>5</v>
+        <v>59</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2</v>
+        <v>60</v>
+      </c>
+      <c r="J8" s="2">
+        <v>4</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="L8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="3">
-        <v>5</v>
+        <v>64</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="3">
+        <v>65</v>
+      </c>
+      <c r="F9" s="2">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3</v>
+        <v>66</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="3">
-        <v>2</v>
+        <v>67</v>
+      </c>
+      <c r="J9" s="2">
+        <v>5</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="L9" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="L9" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="3">
+        <v>71</v>
+      </c>
+      <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="3">
-        <v>5</v>
+        <v>72</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H10" s="3">
-        <v>4</v>
+        <v>73</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J10" s="3">
+        <v>74</v>
+      </c>
+      <c r="J10" s="2">
         <v>2</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L10" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="L10" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1</v>
+        <v>78</v>
+      </c>
+      <c r="D11" s="2">
+        <v>4</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="3">
+        <v>79</v>
+      </c>
+      <c r="F11" s="2">
         <v>5</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" s="3">
-        <v>4</v>
+        <v>80</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J11" s="3">
+        <v>81</v>
+      </c>
+      <c r="J11" s="2">
         <v>3</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L11" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="3">
+        <v>85</v>
+      </c>
+      <c r="D12" s="2">
         <v>3</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="3">
-        <v>4</v>
+        <v>86</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H12" s="3">
-        <v>5</v>
+        <v>87</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="J12" s="3">
-        <v>2</v>
+        <v>88</v>
+      </c>
+      <c r="J12" s="2">
+        <v>5</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="L12" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="3">
+        <v>92</v>
+      </c>
+      <c r="D13" s="2">
         <v>3</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F13" s="3">
+        <v>93</v>
+      </c>
+      <c r="F13" s="2">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="3">
+        <v>94</v>
+      </c>
+      <c r="H13" s="2">
         <v>5</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J13" s="3">
-        <v>2</v>
+        <v>95</v>
+      </c>
+      <c r="J13" s="2">
+        <v>4</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="L13" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="L13" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="3">
-        <v>5</v>
+        <v>99</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F14" s="3">
+        <v>100</v>
+      </c>
+      <c r="F14" s="2">
         <v>4</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H14" s="3">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="H14" s="2">
+        <v>5</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J14" s="3">
-        <v>2</v>
+        <v>101</v>
+      </c>
+      <c r="J14" s="2">
+        <v>3</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="L14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D15" s="3">
-        <v>2</v>
+        <v>105</v>
+      </c>
+      <c r="D15" s="2">
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F15" s="3">
+        <v>106</v>
+      </c>
+      <c r="F15" s="2">
         <v>5</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H15" s="3">
-        <v>3</v>
+        <v>107</v>
+      </c>
+      <c r="H15" s="2">
+        <v>2</v>
       </c>
       <c r="I15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="J15" s="3">
-        <v>4</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="L15" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="L15" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="3">
-        <v>1</v>
+        <v>111</v>
+      </c>
+      <c r="D16" s="2">
+        <v>5</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F16" s="3">
-        <v>2</v>
+        <v>112</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H16" s="3">
+        <v>113</v>
+      </c>
+      <c r="H16" s="2">
         <v>4</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J16" s="3">
-        <v>5</v>
+        <v>114</v>
+      </c>
+      <c r="J16" s="2">
+        <v>2</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="L16" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="L16" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" s="3">
-        <v>4</v>
+        <v>118</v>
+      </c>
+      <c r="D17" s="2">
+        <v>5</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2</v>
+        <v>119</v>
+      </c>
+      <c r="F17" s="2">
+        <v>4</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" s="2">
+        <v>3</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H17" s="3">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J17" s="3">
-        <v>5</v>
+      <c r="J17" s="2">
+        <v>1</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L17" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="L17" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D18" s="3">
-        <v>3</v>
+        <v>124</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F18" s="3">
+        <v>125</v>
+      </c>
+      <c r="F18" s="2">
         <v>2</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H18" s="3">
-        <v>4</v>
+        <v>126</v>
+      </c>
+      <c r="H18" s="2">
+        <v>3</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="J18" s="3">
-        <v>1</v>
+        <v>127</v>
+      </c>
+      <c r="J18" s="2">
+        <v>5</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="L18" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="L18" s="2">
+        <v>4</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1</v>
+        <v>131</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F19" s="3">
-        <v>5</v>
+        <v>132</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H19" s="3">
+        <v>133</v>
+      </c>
+      <c r="H19" s="2">
         <v>3</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="J19" s="3">
+        <v>134</v>
+      </c>
+      <c r="J19" s="2">
         <v>4</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="L19" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="L19" s="2">
+        <v>5</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D20" s="3">
-        <v>5</v>
+        <v>138</v>
+      </c>
+      <c r="D20" s="2">
+        <v>4</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F20" s="3">
-        <v>4</v>
+        <v>139</v>
+      </c>
+      <c r="F20" s="2">
+        <v>2</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H20" s="3">
-        <v>2</v>
+        <v>140</v>
+      </c>
+      <c r="H20" s="2">
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="J20" s="3">
+        <v>141</v>
+      </c>
+      <c r="J20" s="2">
         <v>3</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L20" s="2">
+        <v>5</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D21" s="3">
-        <v>3</v>
+        <v>145</v>
+      </c>
+      <c r="D21" s="2">
+        <v>4</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F21" s="3">
-        <v>2</v>
+        <v>146</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H21" s="3">
-        <v>4</v>
+        <v>147</v>
+      </c>
+      <c r="H21" s="2">
+        <v>3</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="J21" s="3">
+        <v>148</v>
+      </c>
+      <c r="J21" s="2">
         <v>5</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="L21" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="L21" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D22" s="3">
-        <v>5</v>
+        <v>152</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1</v>
+        <v>153</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2</v>
+        <v>154</v>
+      </c>
+      <c r="H22" s="2">
+        <v>4</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="3">
+        <v>155</v>
+      </c>
+      <c r="J22" s="2">
         <v>3</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="L22" s="3">
-        <v>4</v>
+        <v>156</v>
+      </c>
+      <c r="L22" s="2">
+        <v>5</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{859BC7A7-1D94-4966-93D1-1C38D5C82847}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{72B59FD3-0C5A-4CC4-B782-D55A8BEC064B}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
